--- a/docs/collections/shizen/metadata/data.xlsx
+++ b/docs/collections/shizen/metadata/data.xlsx
@@ -710,7 +710,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>残巻 断簡</t>
+          <t>第一 私制字書巻一</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/7024d39c-59dd-40e4-b47a-b8956348d240.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/97e28457-a2b7-40ec-87d0-f976de8fe10a.json</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>7024d39c-59dd-40e4-b47a-b8956348d240</t>
+          <t>97e28457-a2b7-40ec-87d0-f976de8fe10a</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/shizen/document/7024d39c-59dd-40e4-b47a-b8956348d240</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/shizen/document/97e28457-a2b7-40ec-87d0-f976de8fe10a</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/7a54520241ab5e0c59533dd7c3fd620f24546141.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4dfa173d682153131fc1c396cfe9f96f3dc850b2.jpg</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/71963</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/71952</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -775,7 +775,7 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/7024d39c-59dd-40e4-b47a-b8956348d240/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/97e28457-a2b7-40ec-87d0-f976de8fe10a/manifest</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -783,13 +783,13 @@
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="n">
-        <v>18</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>第一 私制字書巻一</t>
+          <t>第二 私制字書巻二</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/97e28457-a2b7-40ec-87d0-f976de8fe10a.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/9cbddbf1-73e1-4d14-a5be-236efa6784e0.json</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>97e28457-a2b7-40ec-87d0-f976de8fe10a</t>
+          <t>9cbddbf1-73e1-4d14-a5be-236efa6784e0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/shizen/document/97e28457-a2b7-40ec-87d0-f976de8fe10a</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/shizen/document/9cbddbf1-73e1-4d14-a5be-236efa6784e0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -826,12 +826,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4dfa173d682153131fc1c396cfe9f96f3dc850b2.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/9af91336c958a76cfa29063044d482382bfe6822.jpg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/71952</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/71953</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -854,7 +854,7 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/97e28457-a2b7-40ec-87d0-f976de8fe10a/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/9cbddbf1-73e1-4d14-a5be-236efa6784e0/manifest</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -868,7 +868,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>第二 私制字書巻二</t>
+          <t>第三 私制字書巻三</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/9cbddbf1-73e1-4d14-a5be-236efa6784e0.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/25825360-d6e9-4b5a-8d29-8229e6fb7848.json</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>9cbddbf1-73e1-4d14-a5be-236efa6784e0</t>
+          <t>25825360-d6e9-4b5a-8d29-8229e6fb7848</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/shizen/document/9cbddbf1-73e1-4d14-a5be-236efa6784e0</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/shizen/document/25825360-d6e9-4b5a-8d29-8229e6fb7848</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/9af91336c958a76cfa29063044d482382bfe6822.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b5baf5d3e778299ed94463314ecd4e5b72ba30d9.jpg</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/71953</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/71954</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -933,7 +933,7 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/9cbddbf1-73e1-4d14-a5be-236efa6784e0/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/25825360-d6e9-4b5a-8d29-8229e6fb7848/manifest</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
@@ -941,13 +941,13 @@
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>第三 私制字書巻三</t>
+          <t>第四 私制儒書巻一</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -959,12 +959,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/25825360-d6e9-4b5a-8d29-8229e6fb7848.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/8cde7a41-3043-4bb8-a9ab-d89a63d74302.json</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>25825360-d6e9-4b5a-8d29-8229e6fb7848</t>
+          <t>8cde7a41-3043-4bb8-a9ab-d89a63d74302</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/shizen/document/25825360-d6e9-4b5a-8d29-8229e6fb7848</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/shizen/document/8cde7a41-3043-4bb8-a9ab-d89a63d74302</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -984,12 +984,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b5baf5d3e778299ed94463314ecd4e5b72ba30d9.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/d1f9bf6a619b63ce1bcfba7be4f62d98e73c3c74.jpg</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/71954</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/71955</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1012,7 +1012,7 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/25825360-d6e9-4b5a-8d29-8229e6fb7848/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/8cde7a41-3043-4bb8-a9ab-d89a63d74302/manifest</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
@@ -1020,13 +1020,13 @@
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>第四 私制儒書巻一</t>
+          <t>第五 私制儒書巻二</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1038,12 +1038,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/8cde7a41-3043-4bb8-a9ab-d89a63d74302.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/2c0edd09-f4f7-400a-9aa9-506f6a020281.json</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8cde7a41-3043-4bb8-a9ab-d89a63d74302</t>
+          <t>2c0edd09-f4f7-400a-9aa9-506f6a020281</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/shizen/document/8cde7a41-3043-4bb8-a9ab-d89a63d74302</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/shizen/document/2c0edd09-f4f7-400a-9aa9-506f6a020281</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1063,12 +1063,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/d1f9bf6a619b63ce1bcfba7be4f62d98e73c3c74.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/eb3146c41ca3e97ed00dc507eec519bf34e5aae7.jpg</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/71955</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/71956</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1091,7 +1091,7 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/8cde7a41-3043-4bb8-a9ab-d89a63d74302/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/2c0edd09-f4f7-400a-9aa9-506f6a020281/manifest</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
@@ -1099,13 +1099,13 @@
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>第五 私制儒書巻二</t>
+          <t>第六 私制儒書巻三</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1117,12 +1117,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/2c0edd09-f4f7-400a-9aa9-506f6a020281.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/1a8618bf-1552-41a1-ac31-14b55adaa85d.json</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2c0edd09-f4f7-400a-9aa9-506f6a020281</t>
+          <t>1a8618bf-1552-41a1-ac31-14b55adaa85d</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/shizen/document/2c0edd09-f4f7-400a-9aa9-506f6a020281</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/shizen/document/1a8618bf-1552-41a1-ac31-14b55adaa85d</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/eb3146c41ca3e97ed00dc507eec519bf34e5aae7.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/548bf46717a366f721480a2b5b5ad41dfea1ec95.jpg</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/71956</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/71957</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1170,7 +1170,7 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/2c0edd09-f4f7-400a-9aa9-506f6a020281/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/1a8618bf-1552-41a1-ac31-14b55adaa85d/manifest</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>
@@ -1178,13 +1178,13 @@
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>第六 私制儒書巻三</t>
+          <t>第七 私制仏書巻</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1196,12 +1196,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/1a8618bf-1552-41a1-ac31-14b55adaa85d.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/29a3ebd1-f59b-46d8-8bfe-5e5ab04fddd9.json</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1a8618bf-1552-41a1-ac31-14b55adaa85d</t>
+          <t>29a3ebd1-f59b-46d8-8bfe-5e5ab04fddd9</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/shizen/document/1a8618bf-1552-41a1-ac31-14b55adaa85d</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/shizen/document/29a3ebd1-f59b-46d8-8bfe-5e5ab04fddd9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/548bf46717a366f721480a2b5b5ad41dfea1ec95.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/05ef88dddc8653bfe5868076f720fa2e5802d2d9.jpg</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/71957</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/71958</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1249,7 +1249,7 @@
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/1a8618bf-1552-41a1-ac31-14b55adaa85d/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/29a3ebd1-f59b-46d8-8bfe-5e5ab04fddd9/manifest</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr"/>
@@ -1257,13 +1257,13 @@
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>第七 私制仏書巻</t>
+          <t>第八 私制韻鑑巻</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1275,12 +1275,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/29a3ebd1-f59b-46d8-8bfe-5e5ab04fddd9.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/cd7d22a0-dde1-4372-bf51-2aede101d8ea.json</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>29a3ebd1-f59b-46d8-8bfe-5e5ab04fddd9</t>
+          <t>cd7d22a0-dde1-4372-bf51-2aede101d8ea</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/shizen/document/29a3ebd1-f59b-46d8-8bfe-5e5ab04fddd9</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/shizen/document/cd7d22a0-dde1-4372-bf51-2aede101d8ea</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1300,12 +1300,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/05ef88dddc8653bfe5868076f720fa2e5802d2d9.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/a032711b94b5be22a664c72ea1322189e7cb6ce5.jpg</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/71958</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/71959</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1328,7 +1328,7 @@
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/29a3ebd1-f59b-46d8-8bfe-5e5ab04fddd9/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/cd7d22a0-dde1-4372-bf51-2aede101d8ea/manifest</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr"/>
@@ -1336,13 +1336,13 @@
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="n">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>第八 私制韻鑑巻</t>
+          <t>第九 私法神書巻上</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/cd7d22a0-dde1-4372-bf51-2aede101d8ea.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/da743702-fefc-41a8-a5e7-f6e737303f49.json</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>cd7d22a0-dde1-4372-bf51-2aede101d8ea</t>
+          <t>da743702-fefc-41a8-a5e7-f6e737303f49</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/shizen/document/cd7d22a0-dde1-4372-bf51-2aede101d8ea</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/shizen/document/da743702-fefc-41a8-a5e7-f6e737303f49</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1379,12 +1379,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/a032711b94b5be22a664c72ea1322189e7cb6ce5.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/80835f6f48a62f69edc43133c9d42928a55cc60f.jpg</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/71959</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/71960</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1407,7 +1407,7 @@
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/cd7d22a0-dde1-4372-bf51-2aede101d8ea/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/da743702-fefc-41a8-a5e7-f6e737303f49/manifest</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr"/>
@@ -1415,13 +1415,13 @@
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>第九 私法神書巻上</t>
+          <t>第二十四 私法世物語巻</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/da743702-fefc-41a8-a5e7-f6e737303f49.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/23f8bc9f-7395-4561-bb43-b660eec7391c.json</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>da743702-fefc-41a8-a5e7-f6e737303f49</t>
+          <t>23f8bc9f-7395-4561-bb43-b660eec7391c</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/shizen/document/da743702-fefc-41a8-a5e7-f6e737303f49</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/shizen/document/23f8bc9f-7395-4561-bb43-b660eec7391c</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1458,12 +1458,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/80835f6f48a62f69edc43133c9d42928a55cc60f.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/97c7970aae3144af3315620d9e743601bebe24b7.jpg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/71960</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/71961</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1486,7 +1486,7 @@
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/da743702-fefc-41a8-a5e7-f6e737303f49/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/23f8bc9f-7395-4561-bb43-b660eec7391c/manifest</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr"/>
@@ -1494,13 +1494,13 @@
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>第二十四 私法世物語巻</t>
+          <t>第二十五 真道哲論巻</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1512,12 +1512,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/23f8bc9f-7395-4561-bb43-b660eec7391c.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/e2b05760-42c2-4677-ba94-df95d960c42a.json</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>23f8bc9f-7395-4561-bb43-b660eec7391c</t>
+          <t>e2b05760-42c2-4677-ba94-df95d960c42a</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/shizen/document/23f8bc9f-7395-4561-bb43-b660eec7391c</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/shizen/document/e2b05760-42c2-4677-ba94-df95d960c42a</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1537,12 +1537,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/97c7970aae3144af3315620d9e743601bebe24b7.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/1e65be02825bc66f99c738a7394e19861c50cc40.jpg</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/71961</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/71962</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1565,7 +1565,7 @@
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/23f8bc9f-7395-4561-bb43-b660eec7391c/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/e2b05760-42c2-4677-ba94-df95d960c42a/manifest</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr"/>
@@ -1573,13 +1573,13 @@
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>第二十五 真道哲論巻</t>
+          <t>残巻 断簡</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/e2b05760-42c2-4677-ba94-df95d960c42a.json</t>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/7024d39c-59dd-40e4-b47a-b8956348d240.json</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>e2b05760-42c2-4677-ba94-df95d960c42a</t>
+          <t>7024d39c-59dd-40e4-b47a-b8956348d240</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/shizen/document/e2b05760-42c2-4677-ba94-df95d960c42a</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/shizen/document/7024d39c-59dd-40e4-b47a-b8956348d240</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/1e65be02825bc66f99c738a7394e19861c50cc40.jpg</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/7a54520241ab5e0c59533dd7c3fd620f24546141.jpg</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/71962</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/71963</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1644,7 +1644,7 @@
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/e2b05760-42c2-4677-ba94-df95d960c42a/manifest</t>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/7024d39c-59dd-40e4-b47a-b8956348d240/manifest</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr"/>
@@ -1652,7 +1652,7 @@
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="n">
-        <v>41</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
